--- a/data/trans_orig/P1418-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1418-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de mala circulación en 2007</t>
+          <t>Población con diagnóstico de mala circulación en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>18143</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14156</t>
+          <t>14303</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32853</t>
+          <t>33501</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23285</t>
+          <t>23500</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46982</t>
+          <t>46689</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>254493</t>
+          <t>254867</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>266944</t>
+          <t>266668</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>227985</t>
+          <t>227337</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>246682</t>
+          <t>246535</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>486866</t>
+          <t>487159</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>510563</t>
+          <t>510348</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19991</t>
+          <t>20271</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42263</t>
+          <t>42741</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55122</t>
+          <t>54239</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85928</t>
+          <t>85795</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80104</t>
+          <t>82104</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117329</t>
+          <t>120554</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>450812</t>
+          <t>450334</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>473084</t>
+          <t>472804</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>418021</t>
+          <t>418154</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>448827</t>
+          <t>449710</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>879695</t>
+          <t>876470</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>916920</t>
+          <t>914920</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18586</t>
+          <t>19893</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>16116</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33245</t>
+          <t>35014</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25132</t>
+          <t>25091</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48662</t>
+          <t>47160</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>298953</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312665</t>
+          <t>312499</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>302167</t>
+          <t>300398</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>320038</t>
+          <t>319296</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>605596</t>
+          <t>607098</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>629126</t>
+          <t>629167</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19213</t>
+          <t>19354</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>20564</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40034</t>
+          <t>40289</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30380</t>
+          <t>30349</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55392</t>
+          <t>55858</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>339458</t>
+          <t>339317</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>352244</t>
+          <t>352248</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>331422</t>
+          <t>331167</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>351076</t>
+          <t>350892</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>674735</t>
+          <t>674269</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>699747</t>
+          <t>699778</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18750</t>
+          <t>19440</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14304</t>
+          <t>13984</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33986</t>
+          <t>32421</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22960</t>
+          <t>22932</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44873</t>
+          <t>44620</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>184558</t>
+          <t>183868</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197440</t>
+          <t>197355</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>173682</t>
+          <t>175247</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>193364</t>
+          <t>193684</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>366103</t>
+          <t>366356</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>388016</t>
+          <t>388044</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17870</t>
+          <t>16915</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>20258</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40649</t>
+          <t>40097</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27599</t>
+          <t>27997</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51571</t>
+          <t>51771</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252941</t>
+          <t>253896</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265933</t>
+          <t>265838</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>237495</t>
+          <t>238047</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>258654</t>
+          <t>257886</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>497384</t>
+          <t>497184</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>521356</t>
+          <t>520958</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20442</t>
+          <t>20835</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41187</t>
+          <t>43015</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44686</t>
+          <t>44024</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73241</t>
+          <t>72644</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69483</t>
+          <t>70482</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>105500</t>
+          <t>108335</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>573840</t>
+          <t>572012</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>594585</t>
+          <t>594192</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>564978</t>
+          <t>565575</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>593533</t>
+          <t>594195</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1147746</t>
+          <t>1144911</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1183763</t>
+          <t>1182764</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50425</t>
+          <t>52056</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>81509</t>
+          <t>83963</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72800</t>
+          <t>72593</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>108468</t>
+          <t>108058</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>131262</t>
+          <t>131317</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>183055</t>
+          <t>178508</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>662286</t>
+          <t>659832</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>693370</t>
+          <t>691739</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>675043</t>
+          <t>675453</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>710711</t>
+          <t>710918</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1344251</t>
+          <t>1348798</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1396044</t>
+          <t>1395989</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,4%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>156679</t>
+          <t>154201</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>208697</t>
+          <t>205646</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>312259</t>
+          <t>308880</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>382390</t>
+          <t>381226</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>477027</t>
+          <t>482505</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>568283</t>
+          <t>564282</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3067846</t>
+          <t>3070897</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3119864</t>
+          <t>3122342</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2996807</t>
+          <t>2997971</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3066938</t>
+          <t>3070317</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6087458</t>
+          <t>6091459</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6178714</t>
+          <t>6173236</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de mala circulación en 2012</t>
+          <t>Población con diagnóstico de mala circulación en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>16553</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>15558</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37262</t>
+          <t>36433</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23412</t>
+          <t>24007</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47178</t>
+          <t>49179</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>277855</t>
+          <t>278185</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290049</t>
+          <t>290080</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>249983</t>
+          <t>250812</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>270941</t>
+          <t>271687</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>534805</t>
+          <t>532804</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>558571</t>
+          <t>557976</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,87%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23674</t>
+          <t>23998</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25257</t>
+          <t>24988</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51189</t>
+          <t>50065</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,47 +4449,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>9,56%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>49633</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>36419</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>65665</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>4,82%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>49633</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>35795</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>65247</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>481853</t>
+          <t>481529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>498360</t>
+          <t>498310</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>472576</t>
+          <t>473700</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>498508</t>
+          <t>498777</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,47 +4562,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>95,23%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>979659</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>963627</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>992873</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>95,18%</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>909</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>979659</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>964045</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>993497</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>95,18%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19570</t>
+          <t>19658</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>14709</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33931</t>
+          <t>34138</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24798</t>
+          <t>24242</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47955</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304476</t>
+          <t>304388</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318737</t>
+          <t>317902</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>307089</t>
+          <t>306882</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>326046</t>
+          <t>326311</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>617111</t>
+          <t>615916</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>640268</t>
+          <t>640824</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24210</t>
+          <t>25072</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42801</t>
+          <t>43186</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68719</t>
+          <t>69588</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55178</t>
+          <t>54586</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88055</t>
+          <t>89835</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>349772</t>
+          <t>348910</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365601</t>
+          <t>365411</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>320232</t>
+          <t>319363</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>346150</t>
+          <t>345765</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>674878</t>
+          <t>673098</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>707755</t>
+          <t>708347</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17754</t>
+          <t>18400</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23453</t>
+          <t>23648</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44964</t>
+          <t>44871</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32062</t>
+          <t>32445</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57870</t>
+          <t>57949</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194864</t>
+          <t>194218</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207990</t>
+          <t>208046</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>174627</t>
+          <t>174720</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>196138</t>
+          <t>195943</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>374339</t>
+          <t>374260</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400147</t>
+          <t>399764</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17601</t>
+          <t>16073</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18197</t>
+          <t>18215</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37825</t>
+          <t>38039</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25751</t>
+          <t>26206</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48991</t>
+          <t>49802</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256380</t>
+          <t>257908</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269794</t>
+          <t>269739</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>240271</t>
+          <t>240057</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>259899</t>
+          <t>259881</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>503086</t>
+          <t>502275</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>526326</t>
+          <t>525871</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17242</t>
+          <t>17994</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40048</t>
+          <t>40157</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>63570</t>
+          <t>63272</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>98716</t>
+          <t>98932</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>87927</t>
+          <t>86721</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>130971</t>
+          <t>129405</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>622740</t>
+          <t>622631</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>645546</t>
+          <t>644794</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>595137</t>
+          <t>594921</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>630283</t>
+          <t>630581</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1225670</t>
+          <t>1227236</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1268714</t>
+          <t>1269920</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5388</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18901</t>
+          <t>18496</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52473</t>
+          <t>51563</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>85575</t>
+          <t>84436</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>62187</t>
+          <t>61355</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>95570</t>
+          <t>96911</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>760197</t>
+          <t>760602</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>773710</t>
+          <t>773773</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>735956</t>
+          <t>737095</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>769058</t>
+          <t>769968</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1505059</t>
+          <t>1503718</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1538442</t>
+          <t>1539274</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>87367</t>
+          <t>88191</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>130977</t>
+          <t>128787</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>311242</t>
+          <t>309986</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>384600</t>
+          <t>383820</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>409172</t>
+          <t>413206</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>496939</t>
+          <t>494468</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3295802</t>
+          <t>3297992</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3339412</t>
+          <t>3338588</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3169452</t>
+          <t>3170232</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3242810</t>
+          <t>3244066</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6483892</t>
+          <t>6486363</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6571659</t>
+          <t>6567625</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de mala circulación en 2016</t>
+          <t>Población con diagnóstico de mala circulación en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11869</t>
+          <t>12322</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>19861</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40374</t>
+          <t>40076</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25355</t>
+          <t>24764</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48657</t>
+          <t>47498</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281892</t>
+          <t>281439</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291645</t>
+          <t>291376</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248329</t>
+          <t>248627</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268413</t>
+          <t>268842</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>533807</t>
+          <t>534966</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>557109</t>
+          <t>557700</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17226</t>
+          <t>16317</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>15579</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38317</t>
+          <t>37992</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22904</t>
+          <t>22655</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48827</t>
+          <t>47296</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>485349</t>
+          <t>486258</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>498391</t>
+          <t>498433</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>484767</t>
+          <t>485092</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>507454</t>
+          <t>507505</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>976832</t>
+          <t>978363</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1002755</t>
+          <t>1003004</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5882</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18266</t>
+          <t>18146</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7991</t>
+          <t>7320</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21761</t>
+          <t>22906</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15685</t>
+          <t>16521</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34657</t>
+          <t>35774</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300299</t>
+          <t>300419</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312700</t>
+          <t>312683</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314548</t>
+          <t>313403</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328318</t>
+          <t>328989</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>620217</t>
+          <t>619100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>639189</t>
+          <t>638353</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15230</t>
+          <t>14798</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11512</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29191</t>
+          <t>30022</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17206</t>
+          <t>17049</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39102</t>
+          <t>38877</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>354734</t>
+          <t>355166</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366665</t>
+          <t>366398</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>358092</t>
+          <t>357261</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>375771</t>
+          <t>376213</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>718145</t>
+          <t>718370</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>740041</t>
+          <t>740198</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6054</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7524</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22689</t>
+          <t>22861</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>7575</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24274</t>
+          <t>23693</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205167</t>
+          <t>206166</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>195898</t>
+          <t>195726</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>211063</t>
+          <t>210882</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>405534</t>
+          <t>406115</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>421566</t>
+          <t>422233</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15578</t>
+          <t>15232</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10584</t>
+          <t>10450</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28842</t>
+          <t>28380</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17658</t>
+          <t>17203</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38680</t>
+          <t>38883</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>247545</t>
+          <t>247891</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259060</t>
+          <t>258961</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244273</t>
+          <t>244735</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>262531</t>
+          <t>262665</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>497558</t>
+          <t>497355</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>518580</t>
+          <t>519035</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13872</t>
+          <t>13476</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32949</t>
+          <t>32641</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55242</t>
+          <t>55351</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88628</t>
+          <t>89523</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73853</t>
+          <t>76579</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>113124</t>
+          <t>114649</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>623609</t>
+          <t>623917</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>642686</t>
+          <t>643082</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>602666</t>
+          <t>601771</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>636052</t>
+          <t>635943</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1234728</t>
+          <t>1233203</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1273999</t>
+          <t>1271273</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9360</t>
+          <t>9694</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26995</t>
+          <t>27759</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48811</t>
+          <t>49534</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81352</t>
+          <t>81531</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>63797</t>
+          <t>62043</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>100926</t>
+          <t>100082</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>751588</t>
+          <t>750824</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>769223</t>
+          <t>768889</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>744815</t>
+          <t>744636</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>777356</t>
+          <t>776633</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1503824</t>
+          <t>1504668</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1540953</t>
+          <t>1542707</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>65743</t>
+          <t>64345</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>104793</t>
+          <t>99877</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>222347</t>
+          <t>223146</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>286891</t>
+          <t>289290</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>298226</t>
+          <t>301375</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>372207</t>
+          <t>373029</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3289557</t>
+          <t>3294473</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3328607</t>
+          <t>3330005</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3257651</t>
+          <t>3255252</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3322195</t>
+          <t>3321396</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6566685</t>
+          <t>6565863</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6640666</t>
+          <t>6637517</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de mala circulación en 2023</t>
+          <t>Población con diagnóstico de mala circulación en 2023 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>10900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12572</t>
+          <t>12950</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>8326</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20086</t>
+          <t>20200</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>300241</t>
+          <t>300543</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309140</t>
+          <t>309470</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>276896</t>
+          <t>276518</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285095</t>
+          <t>284670</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>580825</t>
+          <t>580711</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>592529</t>
+          <t>592585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20564</t>
+          <t>20220</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21462</t>
+          <t>22338</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39077</t>
+          <t>38991</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31613</t>
+          <t>31552</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53525</t>
+          <t>54000</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496829</t>
+          <t>497173</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>510770</t>
+          <t>511108</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>473756</t>
+          <t>473842</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491371</t>
+          <t>490495</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>976701</t>
+          <t>976226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>998613</t>
+          <t>998674</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12662</t>
+          <t>13433</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27003</t>
+          <t>27607</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21400</t>
+          <t>21676</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37153</t>
+          <t>36167</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37548</t>
+          <t>37462</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58738</t>
+          <t>58431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>289047</t>
+          <t>288443</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>303388</t>
+          <t>302617</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>311975</t>
+          <t>312961</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327728</t>
+          <t>327452</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>606440</t>
+          <t>606747</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>627630</t>
+          <t>627716</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7395</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21227</t>
+          <t>21856</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12955</t>
+          <t>13003</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29938</t>
+          <t>30452</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23731</t>
+          <t>24319</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47095</t>
+          <t>46691</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>291330</t>
+          <t>290701</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>305162</t>
+          <t>305189</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>445780</t>
+          <t>445266</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>462763</t>
+          <t>462715</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>741179</t>
+          <t>741583</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>764543</t>
+          <t>763955</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>17561</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28493</t>
+          <t>28845</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22095</t>
+          <t>21567</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35168</t>
+          <t>34966</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168840</t>
+          <t>168965</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175655</t>
+          <t>175755</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>179481</t>
+          <t>179129</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>190803</t>
+          <t>190413</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>351548</t>
+          <t>351750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>364621</t>
+          <t>365149</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16159</t>
+          <t>16585</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29297</t>
+          <t>29674</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30361</t>
+          <t>30122</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46501</t>
+          <t>46408</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49976</t>
+          <t>50456</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70730</t>
+          <t>71138</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>240339</t>
+          <t>239962</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>253477</t>
+          <t>253051</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>209886</t>
+          <t>209979</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>226026</t>
+          <t>226265</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>455293</t>
+          <t>454885</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>476047</t>
+          <t>475567</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,41%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29019</t>
+          <t>29155</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55220</t>
+          <t>56576</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49946</t>
+          <t>43646</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>148514</t>
+          <t>148044</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90715</t>
+          <t>89593</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>177513</t>
+          <t>180666</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>564819</t>
+          <t>563463</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>591020</t>
+          <t>590884</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>697925</t>
+          <t>698395</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>796493</t>
+          <t>802793</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1288966</t>
+          <t>1285813</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1375764</t>
+          <t>1376886</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9743</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33947</t>
+          <t>33884</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37230</t>
+          <t>37402</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65918</t>
+          <t>65347</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44851</t>
+          <t>44842</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>92018</t>
+          <t>94301</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>894773</t>
+          <t>894836</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>919163</t>
+          <t>918977</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>648794</t>
+          <t>649365</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>677482</t>
+          <t>677310</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1551415</t>
+          <t>1549132</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1598582</t>
+          <t>1598591</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>108705</t>
+          <t>109528</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>162460</t>
+          <t>163291</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>246863</t>
+          <t>251747</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>339833</t>
+          <t>340066</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>387436</t>
+          <t>379743</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>493400</t>
+          <t>483252</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3292120</t>
+          <t>3291289</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3345875</t>
+          <t>3345052</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3312826</t>
+          <t>3312593</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3405796</t>
+          <t>3400912</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6613839</t>
+          <t>6623987</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6719803</t>
+          <t>6727496</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1418-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1418-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18143</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14303</t>
+          <t>15086</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33501</t>
+          <t>34077</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23500</t>
+          <t>24188</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46689</t>
+          <t>46368</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>254867</t>
+          <t>254711</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>266668</t>
+          <t>267312</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>227337</t>
+          <t>226761</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>246535</t>
+          <t>245752</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>487159</t>
+          <t>487480</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>510348</t>
+          <t>509660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20271</t>
+          <t>19749</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42741</t>
+          <t>42435</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54239</t>
+          <t>52893</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85795</t>
+          <t>85429</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82104</t>
+          <t>79789</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120554</t>
+          <t>118931</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>450334</t>
+          <t>450640</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>472804</t>
+          <t>473326</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>418154</t>
+          <t>418520</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>449710</t>
+          <t>451056</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>876470</t>
+          <t>878093</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>914920</t>
+          <t>917235</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,0%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19893</t>
+          <t>18935</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16116</t>
+          <t>15719</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35014</t>
+          <t>35468</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25091</t>
+          <t>25597</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47160</t>
+          <t>46858</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>298953</t>
+          <t>299911</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312499</t>
+          <t>312528</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>300398</t>
+          <t>299944</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>319296</t>
+          <t>319693</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>607098</t>
+          <t>607400</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>629167</t>
+          <t>628661</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19354</t>
+          <t>20066</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20564</t>
+          <t>20265</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40289</t>
+          <t>40698</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30349</t>
+          <t>31227</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55858</t>
+          <t>54228</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>339317</t>
+          <t>338605</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>352248</t>
+          <t>352133</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>331167</t>
+          <t>330758</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>350892</t>
+          <t>351191</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>674269</t>
+          <t>675899</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>699778</t>
+          <t>698900</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19440</t>
+          <t>18355</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13984</t>
+          <t>14801</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32421</t>
+          <t>31786</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22932</t>
+          <t>22767</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44620</t>
+          <t>44981</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>183868</t>
+          <t>184953</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197355</t>
+          <t>197467</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175247</t>
+          <t>175882</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>193684</t>
+          <t>192867</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>366356</t>
+          <t>365995</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>388044</t>
+          <t>388209</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16915</t>
+          <t>17119</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20258</t>
+          <t>19778</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40097</t>
+          <t>40930</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27997</t>
+          <t>26957</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51771</t>
+          <t>50797</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253896</t>
+          <t>253692</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265838</t>
+          <t>265891</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>238047</t>
+          <t>237214</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>257886</t>
+          <t>258366</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>497184</t>
+          <t>498158</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>520958</t>
+          <t>521998</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20835</t>
+          <t>19816</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43015</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44024</t>
+          <t>45079</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72644</t>
+          <t>72215</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70482</t>
+          <t>70930</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108335</t>
+          <t>107805</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>572012</t>
+          <t>572023</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>594192</t>
+          <t>595211</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>565575</t>
+          <t>566004</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>594195</t>
+          <t>593140</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1144911</t>
+          <t>1145441</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1182764</t>
+          <t>1182316</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52056</t>
+          <t>51547</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>83963</t>
+          <t>83012</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72593</t>
+          <t>72002</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>108058</t>
+          <t>110619</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>131317</t>
+          <t>132832</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>178508</t>
+          <t>180526</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>659832</t>
+          <t>660783</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>691739</t>
+          <t>692248</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>675453</t>
+          <t>672892</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>710918</t>
+          <t>711509</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1348798</t>
+          <t>1346780</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1395989</t>
+          <t>1394474</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,3%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>154201</t>
+          <t>156040</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>205646</t>
+          <t>206738</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>308880</t>
+          <t>309379</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>381226</t>
+          <t>378888</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>482505</t>
+          <t>475182</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>564282</t>
+          <t>565293</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3070897</t>
+          <t>3069805</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3122342</t>
+          <t>3120503</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2997971</t>
+          <t>3000309</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3070317</t>
+          <t>3069818</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6091459</t>
+          <t>6090448</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6173236</t>
+          <t>6180559</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16553</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15558</t>
+          <t>15840</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>35408</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24007</t>
+          <t>23626</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49179</t>
+          <t>46957</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>278185</t>
+          <t>278563</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290080</t>
+          <t>289994</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250812</t>
+          <t>251837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>271687</t>
+          <t>271405</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>532804</t>
+          <t>535026</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>557976</t>
+          <t>558357</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>7258</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23998</t>
+          <t>24858</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24988</t>
+          <t>25038</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50065</t>
+          <t>51402</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36419</t>
+          <t>37415</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65665</t>
+          <t>66649</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>481529</t>
+          <t>480669</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>498310</t>
+          <t>498269</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>473700</t>
+          <t>472363</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>498777</t>
+          <t>498727</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>963627</t>
+          <t>962643</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>992873</t>
+          <t>991877</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19658</t>
+          <t>20256</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14709</t>
+          <t>14690</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34138</t>
+          <t>34618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24242</t>
+          <t>23925</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>47236</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304388</t>
+          <t>303790</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317902</t>
+          <t>317893</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>306882</t>
+          <t>306402</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>326311</t>
+          <t>326330</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>615916</t>
+          <t>617830</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>640824</t>
+          <t>641141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25072</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43186</t>
+          <t>41645</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69588</t>
+          <t>71152</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54586</t>
+          <t>56087</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89835</t>
+          <t>89889</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>348910</t>
+          <t>349303</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365411</t>
+          <t>365650</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>319363</t>
+          <t>317799</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>345765</t>
+          <t>347306</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>673098</t>
+          <t>673044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>708347</t>
+          <t>706846</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18400</t>
+          <t>18524</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23648</t>
+          <t>24165</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44871</t>
+          <t>45737</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32445</t>
+          <t>32989</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57949</t>
+          <t>57015</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194218</t>
+          <t>194094</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208046</t>
+          <t>207976</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>174720</t>
+          <t>173854</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>195943</t>
+          <t>195426</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>374260</t>
+          <t>375194</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>399764</t>
+          <t>399220</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,37%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16073</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18215</t>
+          <t>18251</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38039</t>
+          <t>38346</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,42 +5821,42 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>13,79%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>25897</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>49810</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
           <t>6,55%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>13,68%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>36155</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>26206</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>49802</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>6,55%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257908</t>
+          <t>257061</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269739</t>
+          <t>268859</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>240057</t>
+          <t>239750</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>259881</t>
+          <t>259845</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,39 +5934,39 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>93,44%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>515922</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>502267</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>526180</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>93,45%</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>494</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>515922</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>502275</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>525871</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>93,45%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
           <t>90,98%</t>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17994</t>
+          <t>18287</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40157</t>
+          <t>41600</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>63272</t>
+          <t>62934</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>98932</t>
+          <t>99026</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>86721</t>
+          <t>86495</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>129405</t>
+          <t>130047</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>622631</t>
+          <t>621188</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>644794</t>
+          <t>644501</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>594921</t>
+          <t>594827</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>630581</t>
+          <t>630919</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1227236</t>
+          <t>1226594</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1269920</t>
+          <t>1270146</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18496</t>
+          <t>19571</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>51563</t>
+          <t>53284</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>84436</t>
+          <t>86739</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>61355</t>
+          <t>61387</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>96911</t>
+          <t>97152</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>760602</t>
+          <t>759527</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>773773</t>
+          <t>773759</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>737095</t>
+          <t>734792</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>769968</t>
+          <t>768247</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1503718</t>
+          <t>1503477</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1539274</t>
+          <t>1539242</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>88191</t>
+          <t>86064</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>128787</t>
+          <t>129575</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>309986</t>
+          <t>312931</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>383820</t>
+          <t>383193</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>413206</t>
+          <t>412841</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>494468</t>
+          <t>497025</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3297992</t>
+          <t>3297204</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3338588</t>
+          <t>3340715</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3170232</t>
+          <t>3170859</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3244066</t>
+          <t>3241121</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6486363</t>
+          <t>6483806</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6567625</t>
+          <t>6567990</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2414</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12322</t>
+          <t>12502</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>20230</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40076</t>
+          <t>40398</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24764</t>
+          <t>23848</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47498</t>
+          <t>47115</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281439</t>
+          <t>281259</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291376</t>
+          <t>291347</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248627</t>
+          <t>248305</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268842</t>
+          <t>268473</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>534966</t>
+          <t>535349</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>557700</t>
+          <t>558616</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16317</t>
+          <t>15873</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>16007</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37992</t>
+          <t>37406</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22655</t>
+          <t>22597</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47296</t>
+          <t>47828</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>486258</t>
+          <t>486702</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>498433</t>
+          <t>498329</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>485092</t>
+          <t>485678</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>507505</t>
+          <t>507077</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>978363</t>
+          <t>977831</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1003004</t>
+          <t>1003062</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5882</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18146</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7320</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22906</t>
+          <t>22150</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16521</t>
+          <t>16087</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35774</t>
+          <t>35415</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300419</t>
+          <t>301049</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312683</t>
+          <t>312945</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>313403</t>
+          <t>314159</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328989</t>
+          <t>328576</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>619100</t>
+          <t>619459</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>638353</t>
+          <t>638787</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14798</t>
+          <t>15056</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11070</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30022</t>
+          <t>29708</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17049</t>
+          <t>18042</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38877</t>
+          <t>39712</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>355166</t>
+          <t>354908</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366398</t>
+          <t>366124</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>357261</t>
+          <t>357575</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>376213</t>
+          <t>376113</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>718370</t>
+          <t>717535</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>740198</t>
+          <t>739205</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22861</t>
+          <t>22578</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7575</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23693</t>
+          <t>24355</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>206166</t>
+          <t>205731</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>195726</t>
+          <t>196009</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>210882</t>
+          <t>210971</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>406115</t>
+          <t>405453</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>422233</t>
+          <t>421503</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15232</t>
+          <t>16556</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10450</t>
+          <t>10212</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28380</t>
+          <t>27458</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17203</t>
+          <t>17428</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38883</t>
+          <t>37091</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>247891</t>
+          <t>246567</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>258961</t>
+          <t>258349</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244735</t>
+          <t>245657</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>262665</t>
+          <t>262903</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>497355</t>
+          <t>499147</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>519035</t>
+          <t>518810</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>12894</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32641</t>
+          <t>32218</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55351</t>
+          <t>55553</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89523</t>
+          <t>90005</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>76579</t>
+          <t>75081</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114649</t>
+          <t>116673</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>623917</t>
+          <t>624340</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>643082</t>
+          <t>643664</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>601771</t>
+          <t>601289</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>635943</t>
+          <t>635741</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1233203</t>
+          <t>1231179</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1271273</t>
+          <t>1272771</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9694</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27759</t>
+          <t>27421</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49534</t>
+          <t>48225</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81531</t>
+          <t>80996</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>62043</t>
+          <t>63573</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>100082</t>
+          <t>102838</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>750824</t>
+          <t>751162</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>768889</t>
+          <t>768781</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>744636</t>
+          <t>745171</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>776633</t>
+          <t>777942</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1504668</t>
+          <t>1501912</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1542707</t>
+          <t>1541177</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>64345</t>
+          <t>64449</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>99877</t>
+          <t>101690</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>223146</t>
+          <t>222423</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>289290</t>
+          <t>285859</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>301375</t>
+          <t>294386</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>373029</t>
+          <t>373711</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3294473</t>
+          <t>3292660</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3330005</t>
+          <t>3329901</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3255252</t>
+          <t>3258683</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3321396</t>
+          <t>3322119</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6565863</t>
+          <t>6565181</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6637517</t>
+          <t>6644506</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>11220</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7679</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12721</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13002</t>
+          <t>13667</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20200</t>
+          <t>20980</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>306120</t>
+          <t>313305</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>300543</t>
+          <t>307625</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309470</t>
+          <t>316499</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>281789</t>
+          <t>307380</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>276518</t>
+          <t>302786</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284670</t>
+          <t>310723</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>587909</t>
+          <t>620685</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>580711</t>
+          <t>613372</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>592585</t>
+          <t>625170</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289468</t>
+          <t>315507</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289468</t>
+          <t>315507</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289468</t>
+          <t>315507</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>600911</t>
+          <t>634352</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>600911</t>
+          <t>634352</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>600911</t>
+          <t>634352</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,27 +11040,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11835</t>
+          <t>12241</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20220</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29899</t>
+          <t>31162</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22338</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38991</t>
+          <t>41652</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,27 +11110,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>41734</t>
+          <t>43402</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31552</t>
+          <t>33386</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54000</t>
+          <t>56228</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -11153,22 +11153,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505558</t>
+          <t>517419</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>497173</t>
+          <t>508951</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>511108</t>
+          <t>523108</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>482934</t>
+          <t>513223</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>473842</t>
+          <t>502733</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>490495</t>
+          <t>520845</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,22 +11223,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>988492</t>
+          <t>1030642</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>976226</t>
+          <t>1017816</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>998674</t>
+          <t>1040658</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512833</t>
+          <t>544385</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512833</t>
+          <t>544385</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512833</t>
+          <t>544385</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1030226</t>
+          <t>1074044</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1030226</t>
+          <t>1074044</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1030226</t>
+          <t>1074044</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18870</t>
+          <t>18568</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13433</t>
+          <t>12527</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27607</t>
+          <t>26716</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28476</t>
+          <t>29238</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21676</t>
+          <t>22054</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36167</t>
+          <t>38321</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,22 +11453,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>47347</t>
+          <t>47807</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37462</t>
+          <t>37838</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58431</t>
+          <t>59413</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>297180</t>
+          <t>297425</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>288443</t>
+          <t>289277</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>302617</t>
+          <t>303466</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>320652</t>
+          <t>327143</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>312961</t>
+          <t>318060</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327452</t>
+          <t>334327</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,27 +11566,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>617831</t>
+          <t>624568</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>606747</t>
+          <t>612962</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>627716</t>
+          <t>634537</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>15152</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7368</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21856</t>
+          <t>24462</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21308</t>
+          <t>23028</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13003</t>
+          <t>16950</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30452</t>
+          <t>30310</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>34140</t>
+          <t>38180</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24319</t>
+          <t>28221</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46691</t>
+          <t>50265</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>299725</t>
+          <t>357993</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>290701</t>
+          <t>348683</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>305189</t>
+          <t>364543</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>454410</t>
+          <t>398933</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>445266</t>
+          <t>391651</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>462715</t>
+          <t>405011</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>754134</t>
+          <t>756927</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>741583</t>
+          <t>744842</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>763955</t>
+          <t>766886</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>22164</t>
+          <t>23896</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17561</t>
+          <t>18582</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28845</t>
+          <t>30301</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>27850</t>
+          <t>29832</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21567</t>
+          <t>23597</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34966</t>
+          <t>38198</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>173056</t>
+          <t>199729</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168965</t>
+          <t>195000</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175755</t>
+          <t>202596</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>185810</t>
+          <t>202643</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>179129</t>
+          <t>196238</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>190413</t>
+          <t>207957</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>358866</t>
+          <t>402371</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>351750</t>
+          <t>394005</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>365149</t>
+          <t>408606</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207974</t>
+          <t>226539</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207974</t>
+          <t>226539</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207974</t>
+          <t>226539</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386716</t>
+          <t>432203</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386716</t>
+          <t>432203</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386716</t>
+          <t>432203</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22438</t>
+          <t>22215</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16585</t>
+          <t>16630</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29674</t>
+          <t>29476</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>37896</t>
+          <t>38952</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30122</t>
+          <t>31720</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46408</t>
+          <t>47848</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>60333</t>
+          <t>61167</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50456</t>
+          <t>51227</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71138</t>
+          <t>71477</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>247198</t>
+          <t>248492</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>239962</t>
+          <t>241231</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>253051</t>
+          <t>254077</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>218491</t>
+          <t>224147</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>209979</t>
+          <t>215251</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>226265</t>
+          <t>231379</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>465690</t>
+          <t>472639</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>454885</t>
+          <t>462329</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>475567</t>
+          <t>482579</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,4%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>40227</t>
+          <t>45569</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29155</t>
+          <t>33897</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56576</t>
+          <t>62186</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>106951</t>
+          <t>124276</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43646</t>
+          <t>108584</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>148044</t>
+          <t>145201</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>147177</t>
+          <t>169845</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>89593</t>
+          <t>148974</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>180666</t>
+          <t>195462</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>579812</t>
+          <t>669623</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>563463</t>
+          <t>653006</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>590884</t>
+          <t>681295</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>739488</t>
+          <t>643426</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>698395</t>
+          <t>622501</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>802793</t>
+          <t>659118</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1319302</t>
+          <t>1313048</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1285813</t>
+          <t>1287431</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1376886</t>
+          <t>1333919</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>620039</t>
+          <t>715192</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>620039</t>
+          <t>715192</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>620039</t>
+          <t>715192</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>846439</t>
+          <t>767702</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>846439</t>
+          <t>767702</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>846439</t>
+          <t>767702</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1466479</t>
+          <t>1482893</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1466479</t>
+          <t>1482893</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1466479</t>
+          <t>1482893</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>21696</t>
+          <t>24344</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9743</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33884</t>
+          <t>34763</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>48308</t>
+          <t>50245</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37402</t>
+          <t>39438</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65347</t>
+          <t>62721</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>70004</t>
+          <t>74589</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44842</t>
+          <t>60441</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94301</t>
+          <t>90769</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>907024</t>
+          <t>773728</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>894836</t>
+          <t>763309</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>918977</t>
+          <t>782058</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>666404</t>
+          <t>779623</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>649365</t>
+          <t>767147</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>677310</t>
+          <t>790430</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1573429</t>
+          <t>1553351</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1549132</t>
+          <t>1537171</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1598591</t>
+          <t>1567499</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714712</t>
+          <t>829868</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714712</t>
+          <t>829868</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714712</t>
+          <t>829868</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643433</t>
+          <t>1627940</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643433</t>
+          <t>1627940</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643433</t>
+          <t>1627940</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>138907</t>
+          <t>149565</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>109528</t>
+          <t>127983</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>163291</t>
+          <t>172386</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>302680</t>
+          <t>328924</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>251747</t>
+          <t>301096</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>340066</t>
+          <t>357002</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>441588</t>
+          <t>478489</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>379743</t>
+          <t>443396</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>483252</t>
+          <t>517126</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3315673</t>
+          <t>3377714</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3291289</t>
+          <t>3354893</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3345052</t>
+          <t>3399296</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3349979</t>
+          <t>3396518</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3312593</t>
+          <t>3368440</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3400912</t>
+          <t>3424346</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6665651</t>
+          <t>6774232</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6623987</t>
+          <t>6735595</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6727496</t>
+          <t>6809325</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3454580</t>
+          <t>3527279</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3454580</t>
+          <t>3527279</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3454580</t>
+          <t>3527279</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3652659</t>
+          <t>3725442</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3652659</t>
+          <t>3725442</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3652659</t>
+          <t>3725442</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7107239</t>
+          <t>7252721</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7107239</t>
+          <t>7252721</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7107239</t>
+          <t>7252721</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
